--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -16669,9 +16669,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1396</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -16719,9 +16725,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -16769,9 +16781,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0935</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -16819,9 +16837,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0799</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -16869,9 +16893,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.07340000000000001</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -16919,9 +16949,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.06279999999999999</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -16969,9 +17005,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1121</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -17019,9 +17061,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0152</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -17069,9 +17117,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1327</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -17119,9 +17173,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L486"/>
+  <dimension ref="A1:L487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>171.01</v>
+        <v>183.08</v>
       </c>
       <c r="C486" t="n">
         <v>159.03</v>
@@ -20810,6 +20810,48 @@
       <c r="L486" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>196.33</v>
+      </c>
+      <c r="C487" t="n">
+        <v>160.12</v>
+      </c>
+      <c r="D487" t="n">
+        <v>147.83</v>
+      </c>
+      <c r="E487" t="n">
+        <v>139.96</v>
+      </c>
+      <c r="F487" t="n">
+        <v>142.18</v>
+      </c>
+      <c r="G487" t="n">
+        <v>143.67</v>
+      </c>
+      <c r="H487" t="n">
+        <v>144.67</v>
+      </c>
+      <c r="I487" t="n">
+        <v>211.75</v>
+      </c>
+      <c r="J487" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="K487" t="n">
+        <v>191.31</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20824,7 +20866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25837,6 +25879,16 @@
       </c>
       <c r="B501" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -25999,28 +26051,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8501715022705194</v>
+        <v>-0.8496462669338762</v>
       </c>
       <c r="J2" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K2" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03430269277233478</v>
+        <v>0.03444821570409573</v>
       </c>
       <c r="M2" t="n">
-        <v>27.5571931558193</v>
+        <v>27.49698545065231</v>
       </c>
       <c r="N2" t="n">
-        <v>1109.855055638855</v>
+        <v>1106.264081696761</v>
       </c>
       <c r="O2" t="n">
-        <v>33.31448717358344</v>
+        <v>33.26054842748027</v>
       </c>
       <c r="P2" t="n">
-        <v>229.5345913130766</v>
+        <v>229.5291446923586</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26071,28 +26123,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1630180770891177</v>
+        <v>-0.1641262537672737</v>
       </c>
       <c r="J3" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K3" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04108185183412016</v>
+        <v>0.04177949515112589</v>
       </c>
       <c r="M3" t="n">
-        <v>4.207464853384209</v>
+        <v>4.204345938646146</v>
       </c>
       <c r="N3" t="n">
-        <v>34.12573314405041</v>
+        <v>34.07066009271824</v>
       </c>
       <c r="O3" t="n">
-        <v>5.841723473774705</v>
+        <v>5.837007803037292</v>
       </c>
       <c r="P3" t="n">
-        <v>167.1443994296526</v>
+        <v>167.1559757011483</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26143,28 +26195,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3534411779127307</v>
+        <v>-0.3533080323310767</v>
       </c>
       <c r="J4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3882403706687596</v>
+        <v>0.3891166818734335</v>
       </c>
       <c r="M4" t="n">
-        <v>2.677344740543477</v>
+        <v>2.672457901660097</v>
       </c>
       <c r="N4" t="n">
-        <v>10.82912445973619</v>
+        <v>10.80706093101687</v>
       </c>
       <c r="O4" t="n">
-        <v>3.29076350711141</v>
+        <v>3.287409455941999</v>
       </c>
       <c r="P4" t="n">
-        <v>156.8365424015728</v>
+        <v>156.8351515318386</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26215,28 +26267,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4237300747398342</v>
+        <v>-0.422989147545558</v>
       </c>
       <c r="J5" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K5" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4379690868162547</v>
+        <v>0.4380740942063042</v>
       </c>
       <c r="M5" t="n">
-        <v>2.797433119915087</v>
+        <v>2.795606815958552</v>
       </c>
       <c r="N5" t="n">
-        <v>12.67576728413979</v>
+        <v>12.65645545092777</v>
       </c>
       <c r="O5" t="n">
-        <v>3.560304380827543</v>
+        <v>3.557591242811318</v>
       </c>
       <c r="P5" t="n">
-        <v>149.3348356321181</v>
+        <v>149.3270957342043</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26287,28 +26339,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2136725402669828</v>
+        <v>-0.2136406232704922</v>
       </c>
       <c r="J6" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K6" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1620807448603597</v>
+        <v>0.162646800100443</v>
       </c>
       <c r="M6" t="n">
-        <v>2.767215773389775</v>
+        <v>2.761643300122309</v>
       </c>
       <c r="N6" t="n">
-        <v>12.98515401892399</v>
+        <v>12.95844815766348</v>
       </c>
       <c r="O6" t="n">
-        <v>3.603491920196851</v>
+        <v>3.599784459889714</v>
       </c>
       <c r="P6" t="n">
-        <v>147.7474442096296</v>
+        <v>147.7471107972559</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26359,28 +26411,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2020998505515091</v>
+        <v>-0.2023767261350023</v>
       </c>
       <c r="J7" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K7" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1701874607091923</v>
+        <v>0.1711944151327628</v>
       </c>
       <c r="M7" t="n">
-        <v>2.485749155704473</v>
+        <v>2.482296130792642</v>
       </c>
       <c r="N7" t="n">
-        <v>10.95628577922068</v>
+        <v>10.9346873613717</v>
       </c>
       <c r="O7" t="n">
-        <v>3.310028063207422</v>
+        <v>3.306763880498833</v>
       </c>
       <c r="P7" t="n">
-        <v>149.6871461860669</v>
+        <v>149.6900384928518</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26431,28 +26483,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2861989856260064</v>
+        <v>-0.2869999548101704</v>
       </c>
       <c r="J8" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K8" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2175564977143365</v>
+        <v>0.2191886373034969</v>
       </c>
       <c r="M8" t="n">
-        <v>2.987432956080731</v>
+        <v>2.984382881431725</v>
       </c>
       <c r="N8" t="n">
-        <v>16.20675407468466</v>
+        <v>16.18131852440946</v>
       </c>
       <c r="O8" t="n">
-        <v>4.02576130373929</v>
+        <v>4.022600965098261</v>
       </c>
       <c r="P8" t="n">
-        <v>154.1994690370369</v>
+        <v>154.2078361475513</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26503,28 +26555,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5651180221533665</v>
+        <v>-0.5635086557026319</v>
       </c>
       <c r="J9" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K9" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09043962293970764</v>
+        <v>0.0903200293692149</v>
       </c>
       <c r="M9" t="n">
-        <v>9.718780988411744</v>
+        <v>9.705934010306082</v>
       </c>
       <c r="N9" t="n">
-        <v>178.7042539838246</v>
+        <v>178.3629193549963</v>
       </c>
       <c r="O9" t="n">
-        <v>13.36803104364381</v>
+        <v>13.35525811637485</v>
       </c>
       <c r="P9" t="n">
-        <v>222.7247730109177</v>
+        <v>222.7079964546219</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26575,28 +26627,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03849223565388377</v>
+        <v>-0.03881907446673431</v>
       </c>
       <c r="J10" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K10" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006206560231680536</v>
+        <v>0.006339030499626475</v>
       </c>
       <c r="M10" t="n">
-        <v>2.716171920998963</v>
+        <v>2.712291625470968</v>
       </c>
       <c r="N10" t="n">
-        <v>13.15365787026108</v>
+        <v>13.12764447583816</v>
       </c>
       <c r="O10" t="n">
-        <v>3.626797191774181</v>
+        <v>3.623209140504886</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3161882815521</v>
+        <v>189.3195960750517</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26647,28 +26699,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04981316442953054</v>
+        <v>-0.0511227170541713</v>
       </c>
       <c r="J11" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K11" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01113529531490753</v>
+        <v>0.01175301055089517</v>
       </c>
       <c r="M11" t="n">
-        <v>2.701977154264966</v>
+        <v>2.70251729057808</v>
       </c>
       <c r="N11" t="n">
-        <v>12.12028588240303</v>
+        <v>12.11623200721518</v>
       </c>
       <c r="O11" t="n">
-        <v>3.481420095651059</v>
+        <v>3.48083783121466</v>
       </c>
       <c r="P11" t="n">
-        <v>195.8244505896555</v>
+        <v>195.8381723899343</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26706,7 +26758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L486"/>
+  <dimension ref="A1:L487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56687,7 +56739,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>-46.902242797166956,168.14344103582098</t>
+          <t>-46.90224163271911,168.1435992340765</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -56738,6 +56790,68 @@
       <c r="L486" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-46.90224035417844,168.1437728982879</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-46.902962509676826,168.14330965186193</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-46.9036823568359,168.14315991370904</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-46.90440177750456,168.14306810486215</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-46.9051202253392,168.1431085467921</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>-46.905838861007844,168.14313942235202</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-46.90655742429318,168.14316387327278</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-46.907269476917165,168.14405449615234</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-46.90799052884399,168.14374797876485</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-46.908708802446114,168.14380927063348</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L487"/>
+  <dimension ref="A1:L489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>171.01</v>
+        <v>161.23</v>
       </c>
       <c r="C485" t="n">
         <v>158.86</v>
@@ -20778,7 +20778,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>183.08</v>
+        <v>161.23</v>
       </c>
       <c r="C486" t="n">
         <v>159.03</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>196.33</v>
+        <v>166.16</v>
       </c>
       <c r="C487" t="n">
         <v>160.12</v>
@@ -20852,6 +20852,90 @@
       <c r="L487" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:26:59+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>222.02</v>
+      </c>
+      <c r="C488" t="n">
+        <v>160.81</v>
+      </c>
+      <c r="D488" t="n">
+        <v>146.52</v>
+      </c>
+      <c r="E488" t="n">
+        <v>138.69</v>
+      </c>
+      <c r="F488" t="n">
+        <v>139.64</v>
+      </c>
+      <c r="G488" t="n">
+        <v>142.26</v>
+      </c>
+      <c r="H488" t="n">
+        <v>144.84</v>
+      </c>
+      <c r="I488" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="J488" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="K488" t="n">
+        <v>191.07</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>232.82</v>
+      </c>
+      <c r="C489" t="n">
+        <v>160.88</v>
+      </c>
+      <c r="D489" t="n">
+        <v>147.08</v>
+      </c>
+      <c r="E489" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="F489" t="n">
+        <v>139.73</v>
+      </c>
+      <c r="G489" t="n">
+        <v>142.15</v>
+      </c>
+      <c r="H489" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="I489" t="n">
+        <v>205.53</v>
+      </c>
+      <c r="J489" t="n">
+        <v>187.04</v>
+      </c>
+      <c r="K489" t="n">
+        <v>191.26</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20866,7 +20950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25889,6 +25973,26 @@
       </c>
       <c r="B502" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -26051,28 +26155,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8496462669338762</v>
+        <v>-0.8577672170778745</v>
       </c>
       <c r="J2" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K2" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03444821570409573</v>
+        <v>0.03509147029473381</v>
       </c>
       <c r="M2" t="n">
-        <v>27.49698545065231</v>
+        <v>27.59565700703844</v>
       </c>
       <c r="N2" t="n">
-        <v>1106.264081696761</v>
+        <v>1111.609713328362</v>
       </c>
       <c r="O2" t="n">
-        <v>33.26054842748027</v>
+        <v>33.34081152774122</v>
       </c>
       <c r="P2" t="n">
-        <v>229.5291446923586</v>
+        <v>229.6130755226363</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26123,28 +26227,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1641262537672737</v>
+        <v>-0.1657186801406093</v>
       </c>
       <c r="J3" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K3" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04177949515112589</v>
+        <v>0.04291374004272852</v>
       </c>
       <c r="M3" t="n">
-        <v>4.204345938646146</v>
+        <v>4.194898395735021</v>
       </c>
       <c r="N3" t="n">
-        <v>34.07066009271824</v>
+        <v>33.94638622359309</v>
       </c>
       <c r="O3" t="n">
-        <v>5.837007803037292</v>
+        <v>5.826352737656131</v>
       </c>
       <c r="P3" t="n">
-        <v>167.1559757011483</v>
+        <v>167.1727454123794</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26195,28 +26299,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3533080323310767</v>
+        <v>-0.3538284458959815</v>
       </c>
       <c r="J4" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K4" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3891166818734335</v>
+        <v>0.3919427011566531</v>
       </c>
       <c r="M4" t="n">
-        <v>2.672457901660097</v>
+        <v>2.664278320308645</v>
       </c>
       <c r="N4" t="n">
-        <v>10.80706093101687</v>
+        <v>10.76473431912228</v>
       </c>
       <c r="O4" t="n">
-        <v>3.287409455941999</v>
+        <v>3.28096545533815</v>
       </c>
       <c r="P4" t="n">
-        <v>156.8351515318386</v>
+        <v>156.8406308719823</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26267,28 +26371,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.422989147545558</v>
+        <v>-0.4227275748536978</v>
       </c>
       <c r="J5" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K5" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4380740942063042</v>
+        <v>0.4399987503400222</v>
       </c>
       <c r="M5" t="n">
-        <v>2.795606815958552</v>
+        <v>2.785509104934828</v>
       </c>
       <c r="N5" t="n">
-        <v>12.65645545092777</v>
+        <v>12.60534134437715</v>
       </c>
       <c r="O5" t="n">
-        <v>3.557591242811318</v>
+        <v>3.550400166794886</v>
       </c>
       <c r="P5" t="n">
-        <v>149.3270957342043</v>
+        <v>149.3243422817769</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26339,28 +26443,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2136406232704922</v>
+        <v>-0.2155869013171038</v>
       </c>
       <c r="J6" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K6" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L6" t="n">
-        <v>0.162646800100443</v>
+        <v>0.1661459484354368</v>
       </c>
       <c r="M6" t="n">
-        <v>2.761643300122309</v>
+        <v>2.762563660559416</v>
       </c>
       <c r="N6" t="n">
-        <v>12.95844815766348</v>
+        <v>12.92828537271413</v>
       </c>
       <c r="O6" t="n">
-        <v>3.599784459889714</v>
+        <v>3.59559249258229</v>
       </c>
       <c r="P6" t="n">
-        <v>147.7471107972559</v>
+        <v>147.7676068816698</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26411,28 +26515,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2023767261350023</v>
+        <v>-0.2040962500120461</v>
       </c>
       <c r="J7" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K7" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1711944151327628</v>
+        <v>0.1746828179796882</v>
       </c>
       <c r="M7" t="n">
-        <v>2.482296130792642</v>
+        <v>2.482280789372856</v>
       </c>
       <c r="N7" t="n">
-        <v>10.9346873613717</v>
+        <v>10.90778700582533</v>
       </c>
       <c r="O7" t="n">
-        <v>3.306763880498833</v>
+        <v>3.302693901321363</v>
       </c>
       <c r="P7" t="n">
-        <v>149.6900384928518</v>
+        <v>149.7081470380838</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26483,28 +26587,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2869999548101704</v>
+        <v>-0.2883929018973618</v>
       </c>
       <c r="J8" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K8" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2191886373034969</v>
+        <v>0.2222962819339768</v>
       </c>
       <c r="M8" t="n">
-        <v>2.984382881431725</v>
+        <v>2.977448231140467</v>
       </c>
       <c r="N8" t="n">
-        <v>16.18131852440946</v>
+        <v>16.12675587511492</v>
       </c>
       <c r="O8" t="n">
-        <v>4.022600965098261</v>
+        <v>4.01581322712037</v>
       </c>
       <c r="P8" t="n">
-        <v>154.2078361475513</v>
+        <v>154.2225051390776</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26555,28 +26659,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5635086557026319</v>
+        <v>-0.5639204063322947</v>
       </c>
       <c r="J9" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K9" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0903200293692149</v>
+        <v>0.0911815078994197</v>
       </c>
       <c r="M9" t="n">
-        <v>9.705934010306082</v>
+        <v>9.672674873291983</v>
       </c>
       <c r="N9" t="n">
-        <v>178.3629193549963</v>
+        <v>177.6324910667344</v>
       </c>
       <c r="O9" t="n">
-        <v>13.35525811637485</v>
+        <v>13.3278839680849</v>
       </c>
       <c r="P9" t="n">
-        <v>222.7079964546219</v>
+        <v>222.7123313723739</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26627,28 +26731,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03881907446673431</v>
+        <v>-0.03950646770520714</v>
       </c>
       <c r="J10" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K10" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006339030499626475</v>
+        <v>0.006621671190991218</v>
       </c>
       <c r="M10" t="n">
-        <v>2.712291625470968</v>
+        <v>2.70472357182388</v>
       </c>
       <c r="N10" t="n">
-        <v>13.12764447583816</v>
+        <v>13.07686937821984</v>
       </c>
       <c r="O10" t="n">
-        <v>3.623209140504886</v>
+        <v>3.616195428654242</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3195960750517</v>
+        <v>189.3268240036565</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26699,28 +26803,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0511227170541713</v>
+        <v>-0.05384665139562799</v>
       </c>
       <c r="J11" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K11" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01175301055089517</v>
+        <v>0.01309160107713481</v>
       </c>
       <c r="M11" t="n">
-        <v>2.70251729057808</v>
+        <v>2.703940292351625</v>
       </c>
       <c r="N11" t="n">
-        <v>12.11623200721518</v>
+        <v>12.11101257033373</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48083783121466</v>
+        <v>3.480088011866041</v>
       </c>
       <c r="P11" t="n">
-        <v>195.8381723899343</v>
+        <v>195.8669473304715</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26758,7 +26862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L487"/>
+  <dimension ref="A1:L489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56677,7 +56781,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>-46.902242797166956,168.14344103582098</t>
+          <t>-46.90224374052703,168.1433128519894</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -56739,7 +56843,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>-46.90224163271911,168.1435992340765</t>
+          <t>-46.90224374052703,168.1433128519894</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -56801,7 +56905,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>-46.90224035417844,168.1437728982879</t>
+          <t>-46.90224326500668,168.14337746817358</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -56852,6 +56956,130 @@
       <c r="L487" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:26:59+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-46.90223787450299,168.1441096102928</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-46.90296244313024,168.1433186956276</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-46.9036824831449,168.14314274343195</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-46.90440189993515,168.1430514586456</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-46.90512047019317,168.14307525391183</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-46.90583899986875,168.14312094066946</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-46.90655740755153,168.14316610159065</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-46.90726975785316,168.14401713854338</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-46.90799049435686,168.14375256660242</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-46.90870882573982,168.14380612463978</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.902236831757754,168.1442511630376</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.902962436379084,168.1433196131111</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.903682429150535,168.14315008339773</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.90440195681151,168.14304372536392</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-46.90512046151741,168.1430764335808</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-46.90583901070173,168.14311949883609</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-46.90655740164268,168.1431668880558</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-46.907270090031844,168.14397296481</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-46.90799057416965,168.1437419490355</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-46.90870880729898,168.14380861521815</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L489"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20934,6 +20934,90 @@
         <v>191.26</v>
       </c>
       <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>246.16</v>
+      </c>
+      <c r="C490" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D490" t="n">
+        <v>146.28</v>
+      </c>
+      <c r="E490" t="n">
+        <v>137.57</v>
+      </c>
+      <c r="F490" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="G490" t="n">
+        <v>142.91</v>
+      </c>
+      <c r="H490" t="n">
+        <v>144.65</v>
+      </c>
+      <c r="I490" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="J490" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="K490" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:21:06+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>246.16</v>
+      </c>
+      <c r="C491" t="n">
+        <v>162.27</v>
+      </c>
+      <c r="D491" t="n">
+        <v>146.99</v>
+      </c>
+      <c r="E491" t="n">
+        <v>137.79</v>
+      </c>
+      <c r="F491" t="n">
+        <v>139.25</v>
+      </c>
+      <c r="G491" t="n">
+        <v>143.02</v>
+      </c>
+      <c r="H491" t="n">
+        <v>144.23</v>
+      </c>
+      <c r="I491" t="n">
+        <v>204.46</v>
+      </c>
+      <c r="J491" t="n">
+        <v>189.03</v>
+      </c>
+      <c r="K491" t="n">
+        <v>192.11</v>
+      </c>
+      <c r="L491" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20950,7 +21034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25993,6 +26077,26 @@
       </c>
       <c r="B504" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -26155,28 +26259,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8577672170778745</v>
+        <v>-0.8254158742224473</v>
       </c>
       <c r="J2" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03509147029473381</v>
+        <v>0.03268464836956475</v>
       </c>
       <c r="M2" t="n">
-        <v>27.59565700703844</v>
+        <v>27.64573305722848</v>
       </c>
       <c r="N2" t="n">
-        <v>1111.609713328362</v>
+        <v>1113.353659881106</v>
       </c>
       <c r="O2" t="n">
-        <v>33.34081152774122</v>
+        <v>33.36695460903056</v>
       </c>
       <c r="P2" t="n">
-        <v>229.6130755226363</v>
+        <v>229.2680855441103</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26227,28 +26331,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1657186801406093</v>
+        <v>-0.1664266726305663</v>
       </c>
       <c r="J3" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K3" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04291374004272852</v>
+        <v>0.04363678067939014</v>
       </c>
       <c r="M3" t="n">
-        <v>4.194898395735021</v>
+        <v>4.181207294490001</v>
       </c>
       <c r="N3" t="n">
-        <v>33.94638622359309</v>
+        <v>33.81152770413026</v>
       </c>
       <c r="O3" t="n">
-        <v>5.826352737656131</v>
+        <v>5.814768069676576</v>
       </c>
       <c r="P3" t="n">
-        <v>167.1727454123794</v>
+        <v>167.1802158787327</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26299,28 +26403,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3538284458959815</v>
+        <v>-0.3544534861880311</v>
       </c>
       <c r="J4" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3919427011566531</v>
+        <v>0.3948787847307889</v>
       </c>
       <c r="M4" t="n">
-        <v>2.664278320308645</v>
+        <v>2.656717096653868</v>
       </c>
       <c r="N4" t="n">
-        <v>10.76473431912228</v>
+        <v>10.72372955636788</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28096545533815</v>
+        <v>3.274710606506761</v>
       </c>
       <c r="P4" t="n">
-        <v>156.8406308719823</v>
+        <v>156.8472259083264</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26371,28 +26475,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4227275748536978</v>
+        <v>-0.4230326336627949</v>
       </c>
       <c r="J5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4399987503400222</v>
+        <v>0.4425726005292762</v>
       </c>
       <c r="M5" t="n">
-        <v>2.785509104934828</v>
+        <v>2.775602442015008</v>
       </c>
       <c r="N5" t="n">
-        <v>12.60534134437715</v>
+        <v>12.55452544856103</v>
       </c>
       <c r="O5" t="n">
-        <v>3.550400166794886</v>
+        <v>3.543236578124727</v>
       </c>
       <c r="P5" t="n">
-        <v>149.3243422817769</v>
+        <v>149.3275615185128</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26443,28 +26547,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2155869013171038</v>
+        <v>-0.2178961425380975</v>
       </c>
       <c r="J6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1661459484354368</v>
+        <v>0.17003587537973</v>
       </c>
       <c r="M6" t="n">
-        <v>2.762563660559416</v>
+        <v>2.765855065487847</v>
       </c>
       <c r="N6" t="n">
-        <v>12.92828537271413</v>
+        <v>12.9082275653793</v>
       </c>
       <c r="O6" t="n">
-        <v>3.59559249258229</v>
+        <v>3.592802188456706</v>
       </c>
       <c r="P6" t="n">
-        <v>147.7676068816698</v>
+        <v>147.7919833616866</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26515,28 +26619,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2040962500120461</v>
+        <v>-0.2051503609598934</v>
       </c>
       <c r="J7" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K7" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1746828179796882</v>
+        <v>0.1773984116155929</v>
       </c>
       <c r="M7" t="n">
-        <v>2.482280789372856</v>
+        <v>2.478368824640896</v>
       </c>
       <c r="N7" t="n">
-        <v>10.90778700582533</v>
+        <v>10.87009046235901</v>
       </c>
       <c r="O7" t="n">
-        <v>3.302693901321363</v>
+        <v>3.296982023360001</v>
       </c>
       <c r="P7" t="n">
-        <v>149.7081470380838</v>
+        <v>149.7192740986582</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26587,28 +26691,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2883929018973618</v>
+        <v>-0.2900944581011118</v>
       </c>
       <c r="J8" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K8" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2222962819339768</v>
+        <v>0.2257203790496676</v>
       </c>
       <c r="M8" t="n">
-        <v>2.977448231140467</v>
+        <v>2.971693973686373</v>
       </c>
       <c r="N8" t="n">
-        <v>16.12675587511492</v>
+        <v>16.07883923668519</v>
       </c>
       <c r="O8" t="n">
-        <v>4.01581322712037</v>
+        <v>4.009842794510178</v>
       </c>
       <c r="P8" t="n">
-        <v>154.2225051390776</v>
+        <v>154.2404691041963</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26659,28 +26763,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5639204063322947</v>
+        <v>-0.5661095234355105</v>
       </c>
       <c r="J9" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K9" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0911815078994197</v>
+        <v>0.09256316755482119</v>
       </c>
       <c r="M9" t="n">
-        <v>9.672674873291983</v>
+        <v>9.644636454653986</v>
       </c>
       <c r="N9" t="n">
-        <v>177.6324910667344</v>
+        <v>176.9263822557872</v>
       </c>
       <c r="O9" t="n">
-        <v>13.3278839680849</v>
+        <v>13.30136768365521</v>
       </c>
       <c r="P9" t="n">
-        <v>222.7123313723739</v>
+        <v>222.7354026637889</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26731,28 +26835,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03950646770520714</v>
+        <v>-0.03925133492924953</v>
       </c>
       <c r="J10" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K10" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006621671190991218</v>
+        <v>0.006595140934653965</v>
       </c>
       <c r="M10" t="n">
-        <v>2.70472357182388</v>
+        <v>2.695345643547786</v>
       </c>
       <c r="N10" t="n">
-        <v>13.07686937821984</v>
+        <v>13.02416734537032</v>
       </c>
       <c r="O10" t="n">
-        <v>3.616195428654242</v>
+        <v>3.608901127125862</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3268240036565</v>
+        <v>189.3241314681512</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26803,28 +26907,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05384665139562799</v>
+        <v>-0.05590383461960764</v>
       </c>
       <c r="J11" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K11" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01309160107713481</v>
+        <v>0.01419265971542594</v>
       </c>
       <c r="M11" t="n">
-        <v>2.703940292351625</v>
+        <v>2.702303130506309</v>
       </c>
       <c r="N11" t="n">
-        <v>12.11101257033373</v>
+        <v>12.08718582043736</v>
       </c>
       <c r="O11" t="n">
-        <v>3.480088011866041</v>
+        <v>3.476663029463361</v>
       </c>
       <c r="P11" t="n">
-        <v>195.8669473304715</v>
+        <v>195.8887300232863</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26862,7 +26966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L489"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57083,6 +57187,130 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.902235543531575,168.1444260069025</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.90296237658293,168.14332773939333</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.903682506285215,168.14313959773236</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.9044020079034,168.1430367785177</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-46.9051205222475,168.14306817589795</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-46.90583893585522,168.14312946059405</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-46.9065574262628,168.14316361111773</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-46.907270092988846,168.14397257157202</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-46.90799046578166,168.14375636795356</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-46.908708764593655,168.14381438287322</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:21:06+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-46.902235543531575,168.1444260069025</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-46.90296230231913,168.1433378317116</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-46.90368243782822,168.14314890376033</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-46.904401986695504,168.14303966211426</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-46.905120507788,168.1430701420129</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-46.9058389250221,168.14313090242743</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-46.90655746762436,168.14315810586172</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-46.90727019549746,168.14395893932212</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-46.9079903780846,168.14376803416914</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-46.90870872479978,168.14381975727915</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L491"/>
+  <dimension ref="A1:L494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21020,6 +21020,132 @@
       <c r="L491" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>232.72</v>
+      </c>
+      <c r="C492" t="n">
+        <v>160.94</v>
+      </c>
+      <c r="D492" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="E492" t="n">
+        <v>137.33</v>
+      </c>
+      <c r="F492" t="n">
+        <v>139.46</v>
+      </c>
+      <c r="G492" t="n">
+        <v>142.73</v>
+      </c>
+      <c r="H492" t="n">
+        <v>144.82</v>
+      </c>
+      <c r="I492" t="n">
+        <v>199.13</v>
+      </c>
+      <c r="J492" t="n">
+        <v>189.24</v>
+      </c>
+      <c r="K492" t="n">
+        <v>191.38</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>215.19</v>
+      </c>
+      <c r="C493" t="n">
+        <v>162.24</v>
+      </c>
+      <c r="D493" t="n">
+        <v>149.59</v>
+      </c>
+      <c r="E493" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="F493" t="n">
+        <v>140.77</v>
+      </c>
+      <c r="G493" t="n">
+        <v>143.96</v>
+      </c>
+      <c r="H493" t="n">
+        <v>145.94</v>
+      </c>
+      <c r="I493" t="n">
+        <v>202.69</v>
+      </c>
+      <c r="J493" t="n">
+        <v>190.41</v>
+      </c>
+      <c r="K493" t="n">
+        <v>193.22</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>215.19</v>
+      </c>
+      <c r="C494" t="n">
+        <v>162.13</v>
+      </c>
+      <c r="D494" t="n">
+        <v>150.09</v>
+      </c>
+      <c r="E494" t="n">
+        <v>140.16</v>
+      </c>
+      <c r="F494" t="n">
+        <v>141.41</v>
+      </c>
+      <c r="G494" t="n">
+        <v>144.17</v>
+      </c>
+      <c r="H494" t="n">
+        <v>145.92</v>
+      </c>
+      <c r="I494" t="n">
+        <v>202.61</v>
+      </c>
+      <c r="J494" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="K494" t="n">
+        <v>194.04</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26097,6 +26223,36 @@
       </c>
       <c r="B506" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -26259,28 +26415,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8254158742224473</v>
+        <v>-0.8084109290349302</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K2" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03268464836956475</v>
+        <v>0.03176870447721047</v>
       </c>
       <c r="M2" t="n">
-        <v>27.64573305722848</v>
+        <v>27.55988392937386</v>
       </c>
       <c r="N2" t="n">
-        <v>1113.353659881106</v>
+        <v>1108.069754881939</v>
       </c>
       <c r="O2" t="n">
-        <v>33.36695460903056</v>
+        <v>33.28768172886089</v>
       </c>
       <c r="P2" t="n">
-        <v>229.2680855441103</v>
+        <v>229.0855957029287</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26331,28 +26487,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1664266726305663</v>
+        <v>-0.167571486498561</v>
       </c>
       <c r="J3" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04363678067939014</v>
+        <v>0.0447843134347774</v>
       </c>
       <c r="M3" t="n">
-        <v>4.181207294490001</v>
+        <v>4.161231593543243</v>
       </c>
       <c r="N3" t="n">
-        <v>33.81152770413026</v>
+        <v>33.61327838818989</v>
       </c>
       <c r="O3" t="n">
-        <v>5.814768069676576</v>
+        <v>5.797695955135099</v>
       </c>
       <c r="P3" t="n">
-        <v>167.1802158787327</v>
+        <v>167.1923772063372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26403,28 +26559,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3544534861880311</v>
+        <v>-0.3524929712598434</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K4" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3948787847307889</v>
+        <v>0.3949266985955157</v>
       </c>
       <c r="M4" t="n">
-        <v>2.656717096653868</v>
+        <v>2.65044830674984</v>
       </c>
       <c r="N4" t="n">
-        <v>10.72372955636788</v>
+        <v>10.68384359002821</v>
       </c>
       <c r="O4" t="n">
-        <v>3.274710606506761</v>
+        <v>3.268614934498741</v>
       </c>
       <c r="P4" t="n">
-        <v>156.8472259083264</v>
+        <v>156.8263746449806</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26475,28 +26631,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4230326336627949</v>
+        <v>-0.4220859460222846</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4425726005292762</v>
+        <v>0.4446062263098536</v>
       </c>
       <c r="M5" t="n">
-        <v>2.775602442015008</v>
+        <v>2.76634725253787</v>
       </c>
       <c r="N5" t="n">
-        <v>12.55452544856103</v>
+        <v>12.48999754444086</v>
       </c>
       <c r="O5" t="n">
-        <v>3.543236578124727</v>
+        <v>3.534119062006947</v>
       </c>
       <c r="P5" t="n">
-        <v>149.3275615185128</v>
+        <v>149.3174880809684</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26547,28 +26703,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2178961425380975</v>
+        <v>-0.2195895204097825</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17003587537973</v>
+        <v>0.1740134143885248</v>
       </c>
       <c r="M6" t="n">
-        <v>2.765855065487847</v>
+        <v>2.759567094843221</v>
       </c>
       <c r="N6" t="n">
-        <v>12.9082275653793</v>
+        <v>12.84542828395367</v>
       </c>
       <c r="O6" t="n">
-        <v>3.592802188456706</v>
+        <v>3.584051936559188</v>
       </c>
       <c r="P6" t="n">
-        <v>147.7919833616866</v>
+        <v>147.8099730178665</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26619,28 +26775,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2051503609598934</v>
+        <v>-0.2058762936442811</v>
       </c>
       <c r="J7" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K7" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1773984116155929</v>
+        <v>0.1803809482667732</v>
       </c>
       <c r="M7" t="n">
-        <v>2.478368824640896</v>
+        <v>2.467504840319641</v>
       </c>
       <c r="N7" t="n">
-        <v>10.87009046235901</v>
+        <v>10.80859301111924</v>
       </c>
       <c r="O7" t="n">
-        <v>3.296982023360001</v>
+        <v>3.287642470086922</v>
       </c>
       <c r="P7" t="n">
-        <v>149.7192740986582</v>
+        <v>149.726982767871</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26691,28 +26847,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2900944581011118</v>
+        <v>-0.2911866763608526</v>
       </c>
       <c r="J8" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K8" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2257203790496676</v>
+        <v>0.2293719691721054</v>
       </c>
       <c r="M8" t="n">
-        <v>2.971693973686373</v>
+        <v>2.957662852706898</v>
       </c>
       <c r="N8" t="n">
-        <v>16.07883923668519</v>
+        <v>15.98757373328954</v>
       </c>
       <c r="O8" t="n">
-        <v>4.009842794510178</v>
+        <v>3.998446414957882</v>
       </c>
       <c r="P8" t="n">
-        <v>154.2404691041963</v>
+        <v>154.2520720810401</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26763,28 +26919,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5661095234355105</v>
+        <v>-0.5734526249614719</v>
       </c>
       <c r="J9" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K9" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09256316755482119</v>
+        <v>0.09580351504364526</v>
       </c>
       <c r="M9" t="n">
-        <v>9.644636454653986</v>
+        <v>9.624743435593778</v>
       </c>
       <c r="N9" t="n">
-        <v>176.9263822557872</v>
+        <v>176.0731921565396</v>
       </c>
       <c r="O9" t="n">
-        <v>13.30136768365521</v>
+        <v>13.26925740787854</v>
       </c>
       <c r="P9" t="n">
-        <v>222.7354026637889</v>
+        <v>222.8133014771438</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26835,28 +26991,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03925133492924953</v>
+        <v>-0.03699744827416344</v>
       </c>
       <c r="J10" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K10" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006595140934653965</v>
+        <v>0.005932975603878066</v>
       </c>
       <c r="M10" t="n">
-        <v>2.695345643547786</v>
+        <v>2.689553646649881</v>
       </c>
       <c r="N10" t="n">
-        <v>13.02416734537032</v>
+        <v>12.96763560003365</v>
       </c>
       <c r="O10" t="n">
-        <v>3.608901127125862</v>
+        <v>3.601060343847858</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3241314681512</v>
+        <v>189.3002071752054</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26907,28 +27063,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05590383461960764</v>
+        <v>-0.05773898083859385</v>
       </c>
       <c r="J11" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K11" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01419265971542594</v>
+        <v>0.01530361504675071</v>
       </c>
       <c r="M11" t="n">
-        <v>2.702303130506309</v>
+        <v>2.694111473144764</v>
       </c>
       <c r="N11" t="n">
-        <v>12.08718582043736</v>
+        <v>12.03427756444981</v>
       </c>
       <c r="O11" t="n">
-        <v>3.476663029463361</v>
+        <v>3.469045627323142</v>
       </c>
       <c r="P11" t="n">
-        <v>195.8887300232863</v>
+        <v>195.9082852174657</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26966,7 +27122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L491"/>
+  <dimension ref="A1:L494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57311,6 +57467,192 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-46.902236841413604,168.14424985236403</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-46.9029624305924,168.1433203995255</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-46.90368241758026,168.1431516562475</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-46.90440203103922,168.14303363277605</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-46.905120487544664,168.14307289457386</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-46.90583895358211,168.1431271012303</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-46.90655740952113,168.14316583943562</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-46.907270720828514,168.14388907404262</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-46.90799035739185,168.1437707868717</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-46.908708795652096,168.14381018821499</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-46.90223853385204,168.1440200912927</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-46.90296230521255,168.14333743850437</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-46.90368218713423,168.14318298217307</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-46.90440188933102,168.14305290044388</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-46.905120361263286,168.14309006531124</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-46.905838832447415,168.14314322354917</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-46.90655729922203,168.14318052011834</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-46.90727036995549,168.1439357382816</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-46.9079902421025,168.14378612335747</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-46.908708617063915,168.14383430750007</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-46.90223853385204,168.1440200912927</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-46.90296231582171,168.1433359967446</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-46.90368213892268,168.14318953571404</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-46.90440175822393,168.14307072631357</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-46.905120299567606,168.14309845406848</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-46.90583881176566,168.1431459761402</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-46.906557301191675,168.14318025796328</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-46.907270377840476,168.143934689647</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-46.907990207613835,168.14379071119512</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-46.90870853747405,168.143845056312</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L494"/>
+  <dimension ref="A1:L499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21030,7 +21030,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>232.72</v>
+        <v>251.54</v>
       </c>
       <c r="C492" t="n">
         <v>160.94</v>
@@ -21072,7 +21072,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>215.19</v>
+        <v>263.71</v>
       </c>
       <c r="C493" t="n">
         <v>162.24</v>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>215.19</v>
+        <v>263.71</v>
       </c>
       <c r="C494" t="n">
         <v>162.13</v>
@@ -21146,6 +21146,216 @@
       <c r="L494" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>265.13</v>
+      </c>
+      <c r="C495" t="n">
+        <v>162.67</v>
+      </c>
+      <c r="D495" t="n">
+        <v>151.07</v>
+      </c>
+      <c r="E495" t="n">
+        <v>140.65</v>
+      </c>
+      <c r="F495" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="G495" t="n">
+        <v>143.77</v>
+      </c>
+      <c r="H495" t="n">
+        <v>145.97</v>
+      </c>
+      <c r="I495" t="n">
+        <v>200.36</v>
+      </c>
+      <c r="J495" t="n">
+        <v>190.42</v>
+      </c>
+      <c r="K495" t="n">
+        <v>194.47</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="C496" t="n">
+        <v>162.97</v>
+      </c>
+      <c r="D496" t="n">
+        <v>149.61</v>
+      </c>
+      <c r="E496" t="n">
+        <v>139.07</v>
+      </c>
+      <c r="F496" t="n">
+        <v>139.51</v>
+      </c>
+      <c r="G496" t="n">
+        <v>141.47</v>
+      </c>
+      <c r="H496" t="n">
+        <v>144.54</v>
+      </c>
+      <c r="I496" t="n">
+        <v>195.91</v>
+      </c>
+      <c r="J496" t="n">
+        <v>188.24</v>
+      </c>
+      <c r="K496" t="n">
+        <v>191.36</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="C497" t="n">
+        <v>162.59</v>
+      </c>
+      <c r="D497" t="n">
+        <v>149.04</v>
+      </c>
+      <c r="E497" t="n">
+        <v>139.68</v>
+      </c>
+      <c r="F497" t="n">
+        <v>138.89</v>
+      </c>
+      <c r="G497" t="n">
+        <v>140.66</v>
+      </c>
+      <c r="H497" t="n">
+        <v>144.13</v>
+      </c>
+      <c r="I497" t="n">
+        <v>194.59</v>
+      </c>
+      <c r="J497" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="K497" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="C498" t="n">
+        <v>161.35</v>
+      </c>
+      <c r="D498" t="n">
+        <v>148.59</v>
+      </c>
+      <c r="E498" t="n">
+        <v>138.01</v>
+      </c>
+      <c r="F498" t="n">
+        <v>138.77</v>
+      </c>
+      <c r="G498" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="H498" t="n">
+        <v>143.32</v>
+      </c>
+      <c r="I498" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="J498" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="K498" t="n">
+        <v>190.71</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="C499" t="n">
+        <v>161.69</v>
+      </c>
+      <c r="D499" t="n">
+        <v>148.24</v>
+      </c>
+      <c r="E499" t="n">
+        <v>138.26</v>
+      </c>
+      <c r="F499" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="G499" t="n">
+        <v>140.09</v>
+      </c>
+      <c r="H499" t="n">
+        <v>143.68</v>
+      </c>
+      <c r="I499" t="n">
+        <v>196.18</v>
+      </c>
+      <c r="J499" t="n">
+        <v>185.02</v>
+      </c>
+      <c r="K499" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21160,7 +21370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26253,6 +26463,56 @@
       </c>
       <c r="B509" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -26415,28 +26675,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8084109290349302</v>
+        <v>-0.6421084816070167</v>
       </c>
       <c r="J2" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K2" t="n">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03176870447721047</v>
+        <v>0.01983601027606063</v>
       </c>
       <c r="M2" t="n">
-        <v>27.55988392937386</v>
+        <v>28.13083352072644</v>
       </c>
       <c r="N2" t="n">
-        <v>1108.069754881939</v>
+        <v>1147.289183907313</v>
       </c>
       <c r="O2" t="n">
-        <v>33.28768172886089</v>
+        <v>33.87165753114709</v>
       </c>
       <c r="P2" t="n">
-        <v>229.0855957029287</v>
+        <v>227.2949840220542</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26487,28 +26747,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.167571486498561</v>
+        <v>-0.1684174262155964</v>
       </c>
       <c r="J3" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0447843134347774</v>
+        <v>0.04618532003379383</v>
       </c>
       <c r="M3" t="n">
-        <v>4.161231593543243</v>
+        <v>4.124621614670421</v>
       </c>
       <c r="N3" t="n">
-        <v>33.61327838818989</v>
+        <v>33.28143852368787</v>
       </c>
       <c r="O3" t="n">
-        <v>5.797695955135099</v>
+        <v>5.769006718984462</v>
       </c>
       <c r="P3" t="n">
-        <v>167.1923772063372</v>
+        <v>167.201412136476</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26559,28 +26819,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3524929712598434</v>
+        <v>-0.3486284404948246</v>
       </c>
       <c r="J4" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K4" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3949266985955157</v>
+        <v>0.393937464117323</v>
       </c>
       <c r="M4" t="n">
-        <v>2.65044830674984</v>
+        <v>2.64195027678908</v>
       </c>
       <c r="N4" t="n">
-        <v>10.68384359002821</v>
+        <v>10.62389506823188</v>
       </c>
       <c r="O4" t="n">
-        <v>3.268614934498741</v>
+        <v>3.259431709398416</v>
       </c>
       <c r="P4" t="n">
-        <v>156.8263746449806</v>
+        <v>156.7851655375498</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26631,28 +26891,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4220859460222846</v>
+        <v>-0.4197819693189144</v>
       </c>
       <c r="J5" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K5" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4446062263098536</v>
+        <v>0.4469793686254331</v>
       </c>
       <c r="M5" t="n">
-        <v>2.76634725253787</v>
+        <v>2.750515910659237</v>
       </c>
       <c r="N5" t="n">
-        <v>12.48999754444086</v>
+        <v>12.38709332482289</v>
       </c>
       <c r="O5" t="n">
-        <v>3.534119062006947</v>
+        <v>3.519530270479697</v>
       </c>
       <c r="P5" t="n">
-        <v>149.3174880809684</v>
+        <v>149.2929262739048</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26703,28 +26963,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2195895204097825</v>
+        <v>-0.224527954113232</v>
       </c>
       <c r="J6" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K6" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1740134143885248</v>
+        <v>0.1830391917102193</v>
       </c>
       <c r="M6" t="n">
-        <v>2.759567094843221</v>
+        <v>2.762609712578065</v>
       </c>
       <c r="N6" t="n">
-        <v>12.84542828395367</v>
+        <v>12.78397651404795</v>
       </c>
       <c r="O6" t="n">
-        <v>3.584051936559188</v>
+        <v>3.575468712497419</v>
       </c>
       <c r="P6" t="n">
-        <v>147.8099730178665</v>
+        <v>147.8626710344991</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26775,28 +27035,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2058762936442811</v>
+        <v>-0.2116069558355702</v>
       </c>
       <c r="J7" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K7" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1803809482667732</v>
+        <v>0.1906510558268598</v>
       </c>
       <c r="M7" t="n">
-        <v>2.467504840319641</v>
+        <v>2.476323720150705</v>
       </c>
       <c r="N7" t="n">
-        <v>10.80859301111924</v>
+        <v>10.80001754831763</v>
       </c>
       <c r="O7" t="n">
-        <v>3.287642470086922</v>
+        <v>3.286338014921415</v>
       </c>
       <c r="P7" t="n">
-        <v>149.726982767871</v>
+        <v>149.7881434576013</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26847,28 +27107,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2911866763608526</v>
+        <v>-0.2953017776366506</v>
       </c>
       <c r="J8" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K8" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2293719691721054</v>
+        <v>0.2378271202194683</v>
       </c>
       <c r="M8" t="n">
-        <v>2.957662852706898</v>
+        <v>2.943217988803547</v>
       </c>
       <c r="N8" t="n">
-        <v>15.98757373328954</v>
+        <v>15.87786953633582</v>
       </c>
       <c r="O8" t="n">
-        <v>3.998446414957882</v>
+        <v>3.984704447802349</v>
       </c>
       <c r="P8" t="n">
-        <v>154.2520720810401</v>
+        <v>154.2959897990436</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26919,28 +27179,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5734526249614719</v>
+        <v>-0.5953953519174271</v>
       </c>
       <c r="J9" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K9" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09580351504364526</v>
+        <v>0.1038893996940594</v>
       </c>
       <c r="M9" t="n">
-        <v>9.624743435593778</v>
+        <v>9.643076675197202</v>
       </c>
       <c r="N9" t="n">
-        <v>176.0731921565396</v>
+        <v>175.5554933147883</v>
       </c>
       <c r="O9" t="n">
-        <v>13.26925740787854</v>
+        <v>13.24973559414633</v>
       </c>
       <c r="P9" t="n">
-        <v>222.8133014771438</v>
+        <v>223.0470552007299</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26991,28 +27251,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03699744827416344</v>
+        <v>-0.03926524694327892</v>
       </c>
       <c r="J10" t="n">
+        <v>498</v>
+      </c>
+      <c r="K10" t="n">
         <v>493</v>
       </c>
-      <c r="K10" t="n">
-        <v>488</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.005932975603878066</v>
+        <v>0.006799207905049953</v>
       </c>
       <c r="M10" t="n">
-        <v>2.689553646649881</v>
+        <v>2.682956258256283</v>
       </c>
       <c r="N10" t="n">
-        <v>12.96763560003365</v>
+        <v>12.88897482818065</v>
       </c>
       <c r="O10" t="n">
-        <v>3.601060343847858</v>
+        <v>3.590121840297436</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3002071752054</v>
+        <v>189.3244027923959</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27063,28 +27323,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05773898083859385</v>
+        <v>-0.06348975958328489</v>
       </c>
       <c r="J11" t="n">
+        <v>498</v>
+      </c>
+      <c r="K11" t="n">
         <v>493</v>
       </c>
-      <c r="K11" t="n">
-        <v>488</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01530361504675071</v>
+        <v>0.0186877601688531</v>
       </c>
       <c r="M11" t="n">
-        <v>2.694111473144764</v>
+        <v>2.693528018880471</v>
       </c>
       <c r="N11" t="n">
-        <v>12.03427756444981</v>
+        <v>12.02041026551431</v>
       </c>
       <c r="O11" t="n">
-        <v>3.469045627323142</v>
+        <v>3.467046331607686</v>
       </c>
       <c r="P11" t="n">
-        <v>195.9082852174657</v>
+        <v>195.9698554244175</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27122,7 +27382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L494"/>
+  <dimension ref="A1:L499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57475,7 +57735,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>-46.902236841413604,168.14424985236403</t>
+          <t>-46.90223502391617,168.14449652114845</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -57537,7 +57797,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>-46.90223853385204,168.1440200912927</t>
+          <t>-46.90223384834266,168.14465603014744</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -57599,7 +57859,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>-46.90223853385204,168.1440200912927</t>
+          <t>-46.90223384834266,168.14465603014744</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -57650,6 +57910,316 @@
       <c r="L494" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-46.902233711161784,168.1446746417158</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-46.90296226374019,168.14334307447436</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-46.90368204442696,168.1432023806544</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-46.904401710986136,168.1430771488696</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-46.90512034873138,168.14309176927756</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-46.90583885115942,168.14314073310965</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-46.90655729626757,168.1431809133509</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-46.90727059960207,168.14390519679924</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-46.90799024111711,168.14378625443857</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-46.9087084957375,168.14385069288412</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-46.90223364643453,168.1446834232305</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-46.90296223480581,168.14334700654643</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-46.90368218520578,168.14318324431474</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-46.90440186330263,168.1430564394033</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-46.905120482724804,168.1430735499455</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-46.905839077668944,168.14311058568427</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-46.90655743709562,168.14316216926497</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-46.90727103817473,168.14384686650135</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-46.90799045592813,168.14375767876427</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-46.90870879759325,168.14380992604885</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-46.90223364643453,168.1446834232305</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-46.902962271456,168.1433420259218</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-46.90368224016651,168.14317577327805</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-46.90440180449733,168.1430644348301</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-46.90512054249071,168.14306542333702</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-46.905839157437796,168.14309996854757</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-46.90655747747231,168.1431567950865</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-46.907271168262454,168.14382956403125</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-46.90799060767104,168.143737492279</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-46.908708939295416,168.1437907879206</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-46.90223364643453,168.1446834232305</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-46.90296239104978,168.14332577335728</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-46.903682283556215,168.14316987509122</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-46.904401965487516,168.1430425457108</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-46.90512055405825,168.14306385044506</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-46.90583918304238,168.1430965605778</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-46.90655755724017,168.14314617780713</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-46.90727121655192,168.14382314114465</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-46.90799073576291,168.1437204517396</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-46.90870886068022,168.14380140564927</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-46.902232602976575,168.14482497600918</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-46.90296235825817,168.1433302297056</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-46.903682317303556,168.14316528761256</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-46.90440194138746,168.14304582252507</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-46.905120541526756,168.14306555441135</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-46.90583921357082,168.1430924972292</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-46.906557521787924,168.14315089659794</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-46.907271011565555,168.14385040564298</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-46.90799077320466,168.14371547065886</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-46.90870885194515,168.1438025853969</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
